--- a/samples/예시데이터_옵션내역.xlsx
+++ b/samples/예시데이터_옵션내역.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:S99"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -410,6 +410,14 @@
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,7 +436,7 @@
         <v>Equipment</v>
       </c>
       <c r="D3" t="str">
-        <v>Region</v>
+        <v>Emission</v>
       </c>
       <c r="E3" t="str">
         <v>Power</v>
@@ -437,10 +445,10 @@
         <v>ATS type</v>
       </c>
       <c r="G3" t="str">
-        <v>CAN SA</v>
+        <v>CAN1(J1939) baudrate</v>
       </c>
       <c r="H3" t="str">
-        <v>Pedal type</v>
+        <v>Accelerator type</v>
       </c>
       <c r="I3" t="str">
         <v>starter control type</v>
@@ -449,6 +457,30 @@
         <v>check engine lamp</v>
       </c>
       <c r="K3" t="str">
+        <v>Parking Brake</v>
+      </c>
+      <c r="L3" t="str">
+        <v>SAC lamp</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Emergency stop</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Oil pressure lamp</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Regeneration demand switch</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Regeneration inhibit switch</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>WIF</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Electric feed pump</v>
+      </c>
+      <c r="S3" t="str">
         <v>예시 옵션 X</v>
       </c>
     </row>
@@ -460,30 +492,54 @@
         <v>EX101</v>
       </c>
       <c r="C4" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D4" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E4">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F4" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G4" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H4" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I4" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J4" t="str">
         <v>CAN type</v>
       </c>
       <c r="K4" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L4" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R4" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S4" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -495,30 +551,54 @@
         <v>EX102</v>
       </c>
       <c r="C5" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D5" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E5">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F5" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G5" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H5" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I5" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J5" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K5" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L5" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P5" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R5" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S5" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -530,30 +610,54 @@
         <v>EX103</v>
       </c>
       <c r="C6" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D6" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F6" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G6" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H6" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I6" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J6" t="str">
         <v>CAN type</v>
       </c>
       <c r="K6" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L6" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M6" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P6" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R6" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S6" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -565,30 +669,54 @@
         <v>EX104</v>
       </c>
       <c r="C7" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D7" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E7">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="F7" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G7" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H7" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I7" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J7" t="str">
         <v>CAN type</v>
       </c>
       <c r="K7" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L7" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M7" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R7" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S7" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -600,30 +728,54 @@
         <v>EX105</v>
       </c>
       <c r="C8" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D8" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E8">
         <v>180</v>
       </c>
       <c r="F8" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC</v>
       </c>
       <c r="G8" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H8" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I8" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J8" t="str">
-        <v>CAN</v>
+        <v>hw type</v>
       </c>
       <c r="K8" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L8" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R8" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S8" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -635,30 +787,54 @@
         <v>EX106</v>
       </c>
       <c r="C9" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D9" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E9">
         <v>40</v>
       </c>
       <c r="F9" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G9" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H9" t="str">
-        <v>예시 Pedal-C</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I9" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J9" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K9" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M9" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R9" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S9" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -670,30 +846,54 @@
         <v>EX107</v>
       </c>
       <c r="C10" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D10" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E10">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="F10" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G10" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H10" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I10" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J10" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K10" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L10" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M10" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R10" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S10" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -705,30 +905,54 @@
         <v>EX108</v>
       </c>
       <c r="C11" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D11" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E11">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F11" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G11" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H11" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I11" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J11" t="str">
         <v>CAN type</v>
       </c>
       <c r="K11" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L11" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R11" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S11" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -740,30 +964,54 @@
         <v>EX109</v>
       </c>
       <c r="C12" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D12" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F12" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G12" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H12" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I12" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J12" t="str">
         <v>HW type</v>
       </c>
       <c r="K12" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L12" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M12" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P12" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R12" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S12" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -775,30 +1023,54 @@
         <v>EX110</v>
       </c>
       <c r="C13" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D13" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E13">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F13" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G13" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H13" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I13" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J13" t="str">
         <v>CAN type</v>
       </c>
       <c r="K13" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L13" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M13" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P13" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R13" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S13" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -810,30 +1082,54 @@
         <v>EX111</v>
       </c>
       <c r="C14" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D14" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F14" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G14" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H14" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I14" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J14" t="str">
         <v>CAN type</v>
       </c>
       <c r="K14" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L14" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P14" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R14" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S14" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -845,30 +1141,54 @@
         <v>EX112</v>
       </c>
       <c r="C15" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D15" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F15" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G15" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H15" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I15" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J15" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K15" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L15" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M15" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R15" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S15" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -880,30 +1200,54 @@
         <v>EX113</v>
       </c>
       <c r="C16" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D16" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E16">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="F16" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G16" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H16" t="str">
-        <v>예시 Pedal-C</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I16" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J16" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R16" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S16" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -915,30 +1259,54 @@
         <v>EX114</v>
       </c>
       <c r="C17" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D17" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E17">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="F17" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G17" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I17" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J17" t="str">
         <v>CAN</v>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P17" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R17" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S17" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -950,30 +1318,54 @@
         <v>EX115</v>
       </c>
       <c r="C18" t="str">
-        <v>굴삭기</v>
+        <v>Loader</v>
       </c>
       <c r="D18" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E18">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F18" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G18" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H18" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I18" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J18" t="str">
         <v>CAN type</v>
       </c>
       <c r="K18" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M18" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R18" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S18" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -985,30 +1377,54 @@
         <v>EX116</v>
       </c>
       <c r="C19" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D19" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E19">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="F19" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G19" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I19" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J19" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P19" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R19" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S19" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1020,30 +1436,54 @@
         <v>EX117</v>
       </c>
       <c r="C20" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D20" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E20">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="F20" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G20" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I20" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J20" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M20" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R20" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S20" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1055,30 +1495,54 @@
         <v>EX118</v>
       </c>
       <c r="C21" t="str">
-        <v>굴삭기</v>
+        <v>Loader</v>
       </c>
       <c r="D21" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E21">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F21" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G21" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H21" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I21" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J21" t="str">
         <v>CAN type</v>
       </c>
       <c r="K21" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L21" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M21" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R21" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S21" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1090,30 +1554,54 @@
         <v>EX119</v>
       </c>
       <c r="C22" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D22" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E22">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="F22" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G22" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I22" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J22" t="str">
         <v>CAN type</v>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P22" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R22" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S22" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1125,30 +1613,54 @@
         <v>EX120</v>
       </c>
       <c r="C23" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D23" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E23">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="F23" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G23" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I23" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J23" t="str">
         <v>CAN type</v>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M23" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P23" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R23" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S23" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1160,30 +1672,54 @@
         <v>EX121</v>
       </c>
       <c r="C24" t="str">
-        <v>굴삭기</v>
+        <v>Loader</v>
       </c>
       <c r="D24" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E24">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="F24" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G24" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H24" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I24" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J24" t="str">
         <v>HW type</v>
       </c>
       <c r="K24" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L24" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M24" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P24" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R24" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S24" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1195,30 +1731,54 @@
         <v>EX122</v>
       </c>
       <c r="C25" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D25" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E25">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="F25" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G25" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I25" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J25" t="str">
         <v>HW type</v>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P25" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R25" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S25" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1230,30 +1790,54 @@
         <v>EX123</v>
       </c>
       <c r="C26" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D26" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E26">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="F26" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G26" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I26" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J26" t="str">
-        <v>hw type</v>
+        <v>CAN</v>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P26" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R26" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S26" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1265,30 +1849,54 @@
         <v>EX124</v>
       </c>
       <c r="C27" t="str">
-        <v>굴삭기</v>
+        <v>Loader</v>
       </c>
       <c r="D27" t="str">
-        <v>한국</v>
+        <v>Korea Stage5</v>
       </c>
       <c r="E27">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="F27" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC</v>
       </c>
       <c r="G27" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H27" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I27" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J27" t="str">
         <v>HW type</v>
       </c>
       <c r="K27" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L27" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M27" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R27" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S27" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1300,30 +1908,54 @@
         <v>EX125</v>
       </c>
       <c r="C28" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D28" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E28">
         <v>90</v>
       </c>
       <c r="F28" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC</v>
       </c>
       <c r="G28" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H28" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I28" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J28" t="str">
         <v>CAN type</v>
       </c>
       <c r="K28" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L28" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M28" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R28" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S28" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1335,30 +1967,54 @@
         <v>EX126</v>
       </c>
       <c r="C29" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D29" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E29">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F29" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G29" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H29" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I29" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J29" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K29" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L29" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M29" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P29" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R29" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S29" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1370,30 +2026,54 @@
         <v>EX127</v>
       </c>
       <c r="C30" t="str">
-        <v>발전기</v>
+        <v>TLS</v>
       </c>
       <c r="D30" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E30">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="F30" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G30" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I30" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J30" t="str">
         <v>CAN type</v>
       </c>
       <c r="K30" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L30" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M30" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P30" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R30" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S30" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1405,30 +2085,54 @@
         <v>EX128</v>
       </c>
       <c r="C31" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D31" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E31">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="F31" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G31" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H31" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I31" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J31" t="str">
         <v>CAN type</v>
       </c>
       <c r="K31" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L31" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P31" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R31" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S31" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1440,30 +2144,54 @@
         <v>EX129</v>
       </c>
       <c r="C32" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D32" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E32">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F32" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G32" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H32" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I32" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J32" t="str">
         <v>CAN type</v>
       </c>
       <c r="K32" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L32" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P32" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R32" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S32" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1475,30 +2203,54 @@
         <v>EX130</v>
       </c>
       <c r="C33" t="str">
-        <v>발전기</v>
+        <v>TLS</v>
       </c>
       <c r="D33" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E33">
-        <v>340</v>
+        <v>115</v>
       </c>
       <c r="F33" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G33" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H33" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I33" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J33" t="str">
         <v>HW type</v>
       </c>
       <c r="K33" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L33" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P33" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R33" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S33" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1510,30 +2262,54 @@
         <v>EX131</v>
       </c>
       <c r="C34" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D34" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E34">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="F34" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G34" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H34" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I34" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J34" t="str">
         <v>CAN type</v>
       </c>
       <c r="K34" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L34" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P34" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R34" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S34" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1545,30 +2321,54 @@
         <v>EX132</v>
       </c>
       <c r="C35" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D35" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E35">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="F35" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G35" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H35" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I35" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J35" t="str">
-        <v>CAN</v>
+        <v>hw type</v>
       </c>
       <c r="K35" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P35" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R35" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S35" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1580,30 +2380,54 @@
         <v>EX133</v>
       </c>
       <c r="C36" t="str">
-        <v>발전기</v>
+        <v>TLS</v>
       </c>
       <c r="D36" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E36">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="F36" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G36" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H36" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I36" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J36" t="str">
         <v>CAN type</v>
       </c>
       <c r="K36" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L36" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M36" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P36" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R36" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S36" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1615,30 +2439,54 @@
         <v>EX134</v>
       </c>
       <c r="C37" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D37" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E37">
         <v>90</v>
       </c>
       <c r="F37" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G37" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H37" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I37" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J37" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K37" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L37" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P37" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R37" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S37" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1650,30 +2498,54 @@
         <v>EX135</v>
       </c>
       <c r="C38" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D38" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E38">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F38" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G38" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H38" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I38" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J38" t="str">
         <v>CAN type</v>
       </c>
       <c r="K38" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L38" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M38" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P38" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R38" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S38" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1685,30 +2557,54 @@
         <v>EX136</v>
       </c>
       <c r="C39" t="str">
-        <v>발전기</v>
+        <v>TLS</v>
       </c>
       <c r="D39" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E39">
-        <v>380</v>
+        <v>95</v>
       </c>
       <c r="F39" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G39" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I39" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J39" t="str">
         <v>HW type</v>
       </c>
       <c r="K39" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L39" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M39" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P39" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R39" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S39" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1720,30 +2616,54 @@
         <v>EX137</v>
       </c>
       <c r="C40" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D40" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F40" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G40" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H40" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I40" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J40" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K40" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L40" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P40" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R40" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S40" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1755,30 +2675,54 @@
         <v>EX138</v>
       </c>
       <c r="C41" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D41" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E41">
         <v>90</v>
       </c>
       <c r="F41" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G41" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H41" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I41" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J41" t="str">
         <v>CAN type</v>
       </c>
       <c r="K41" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P41" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R41" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S41" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1790,30 +2734,54 @@
         <v>EX139</v>
       </c>
       <c r="C42" t="str">
-        <v>굴삭기</v>
+        <v>Generator</v>
       </c>
       <c r="D42" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E42">
-        <v>105</v>
+        <v>340</v>
       </c>
       <c r="F42" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G42" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H42" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I42" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J42" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P42" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R42" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S42" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1825,30 +2793,54 @@
         <v>EX140</v>
       </c>
       <c r="C43" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D43" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E43">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F43" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G43" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H43" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I43" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J43" t="str">
         <v>CAN type</v>
       </c>
       <c r="K43" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L43" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M43" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P43" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R43" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S43" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1860,30 +2852,54 @@
         <v>EX141</v>
       </c>
       <c r="C44" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D44" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E44">
         <v>50</v>
       </c>
       <c r="F44" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G44" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H44" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I44" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J44" t="str">
-        <v>CAN</v>
+        <v>hw type</v>
       </c>
       <c r="K44" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M44" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P44" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R44" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S44" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1895,30 +2911,54 @@
         <v>EX142</v>
       </c>
       <c r="C45" t="str">
-        <v>굴삭기</v>
+        <v>Generator</v>
       </c>
       <c r="D45" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E45">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="F45" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G45" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H45" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I45" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J45" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P45" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R45" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S45" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -1930,30 +2970,54 @@
         <v>EX143</v>
       </c>
       <c r="C46" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D46" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E46">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F46" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G46" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H46" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I46" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J46" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K46" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L46" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P46" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R46" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S46" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -1965,30 +3029,54 @@
         <v>EX144</v>
       </c>
       <c r="C47" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D47" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F47" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G47" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H47" t="str">
-        <v>예시 Pedal-C</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I47" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J47" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K47" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L47" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M47" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P47" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R47" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S47" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2000,30 +3088,54 @@
         <v>EX145</v>
       </c>
       <c r="C48" t="str">
-        <v>굴삭기</v>
+        <v>Generator</v>
       </c>
       <c r="D48" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E48">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="F48" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G48" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H48" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I48" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J48" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P48" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R48" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S48" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2035,30 +3147,54 @@
         <v>EX146</v>
       </c>
       <c r="C49" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D49" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E49">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F49" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G49" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H49" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I49" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J49" t="str">
         <v>CAN type</v>
       </c>
       <c r="K49" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L49" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M49" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P49" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R49" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S49" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2070,30 +3206,54 @@
         <v>EX147</v>
       </c>
       <c r="C50" t="str">
-        <v>지게차</v>
+        <v>Forklift</v>
       </c>
       <c r="D50" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E50">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F50" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G50" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H50" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I50" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J50" t="str">
         <v>CAN type</v>
       </c>
       <c r="K50" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L50" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M50" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P50" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R50" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S50" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2105,30 +3265,54 @@
         <v>EX148</v>
       </c>
       <c r="C51" t="str">
-        <v>굴삭기</v>
+        <v>Generator</v>
       </c>
       <c r="D51" t="str">
-        <v>유럽</v>
+        <v>EU Stage5</v>
       </c>
       <c r="E51">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="F51" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G51" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H51" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I51" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J51" t="str">
         <v>CAN type</v>
       </c>
       <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P51" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R51" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S51" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2140,30 +3324,54 @@
         <v>EX149</v>
       </c>
       <c r="C52" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D52" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E52">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="F52" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G52" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I52" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J52" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P52" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R52" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S52" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2175,30 +3383,54 @@
         <v>EX150</v>
       </c>
       <c r="C53" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D53" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E53">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F53" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G53" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I53" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J53" t="str">
         <v>hw type</v>
       </c>
       <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P53" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R53" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S53" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2210,30 +3442,54 @@
         <v>EX151</v>
       </c>
       <c r="C54" t="str">
-        <v>지게차</v>
+        <v>TLS</v>
       </c>
       <c r="D54" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E54">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="F54" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G54" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H54" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I54" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J54" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K54" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L54" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M54" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P54" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R54" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S54" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2245,30 +3501,54 @@
         <v>EX152</v>
       </c>
       <c r="C55" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D55" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E55">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="F55" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G55" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I55" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J55" t="str">
         <v>CAN type</v>
       </c>
       <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P55" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R55" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S55" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2280,30 +3560,54 @@
         <v>EX153</v>
       </c>
       <c r="C56" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D56" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="F56" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G56" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I56" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J56" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M56" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P56" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R56" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S56" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2315,30 +3619,54 @@
         <v>EX154</v>
       </c>
       <c r="C57" t="str">
-        <v>지게차</v>
+        <v>TLS</v>
       </c>
       <c r="D57" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E57">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F57" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G57" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H57" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I57" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J57" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K57" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L57" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P57" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R57" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S57" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2350,30 +3678,54 @@
         <v>EX155</v>
       </c>
       <c r="C58" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D58" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E58">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="F58" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G58" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I58" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J58" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P58" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R58" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S58" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2385,30 +3737,54 @@
         <v>EX156</v>
       </c>
       <c r="C59" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D59" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E59">
         <v>360</v>
       </c>
       <c r="F59" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G59" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H59" t="str">
-        <v>예시 Pedal-C</v>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I59" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J59" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P59" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R59" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S59" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2420,30 +3796,54 @@
         <v>EX157</v>
       </c>
       <c r="C60" t="str">
-        <v>지게차</v>
+        <v>TLS</v>
       </c>
       <c r="D60" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E60">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F60" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G60" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H60" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I60" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J60" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K60" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M60" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P60" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R60" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S60" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2455,30 +3855,54 @@
         <v>EX158</v>
       </c>
       <c r="C61" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D61" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E61">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="F61" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G61" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I61" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J61" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P61" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R61" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S61" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2490,30 +3914,54 @@
         <v>EX159</v>
       </c>
       <c r="C62" t="str">
-        <v>발전기</v>
+        <v>Generator</v>
       </c>
       <c r="D62" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E62">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="F62" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G62" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>CAN (TSC1)</v>
       </c>
       <c r="I62" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J62" t="str">
-        <v>hw type</v>
+        <v>CAN</v>
       </c>
       <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P62" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R62" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S62" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2525,30 +3973,54 @@
         <v>EX160</v>
       </c>
       <c r="C63" t="str">
-        <v>지게차</v>
+        <v>TLS</v>
       </c>
       <c r="D63" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E63">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F63" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G63" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H63" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I63" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J63" t="str">
         <v>HW type</v>
       </c>
       <c r="K63" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L63" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P63" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R63" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S63" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2560,30 +4032,54 @@
         <v>EX161</v>
       </c>
       <c r="C64" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D64" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E64">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="F64" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G64" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H64" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I64" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J64" t="str">
-        <v>CAN type</v>
+        <v>HW type</v>
       </c>
       <c r="K64" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L64" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P64" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R64" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S64" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2595,30 +4091,54 @@
         <v>EX162</v>
       </c>
       <c r="C65" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D65" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E65">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F65" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G65" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H65" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I65" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J65" t="str">
         <v>HW type</v>
       </c>
       <c r="K65" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L65" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M65" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P65" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R65" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S65" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2630,30 +4150,54 @@
         <v>EX163</v>
       </c>
       <c r="C66" t="str">
-        <v>지게차</v>
+        <v>Loader</v>
       </c>
       <c r="D66" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E66">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="F66" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC</v>
       </c>
       <c r="G66" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H66" t="str">
-        <v>예시 Pedal-B</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I66" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J66" t="str">
         <v>HW type</v>
       </c>
       <c r="K66" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L66" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M66" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R66" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S66" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2665,30 +4209,54 @@
         <v>EX164</v>
       </c>
       <c r="C67" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D67" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E67">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="F67" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G67" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H67" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I67" t="str">
-        <v>예시 Starter-B</v>
+        <v>ECU control</v>
       </c>
       <c r="J67" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K67" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P67" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R67" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S67" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2700,30 +4268,54 @@
         <v>EX165</v>
       </c>
       <c r="C68" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D68" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E68">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F68" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G68" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H68" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I68" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J68" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K68" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L68" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P68" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R68" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S68" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2735,30 +4327,54 @@
         <v>EX166</v>
       </c>
       <c r="C69" t="str">
-        <v>지게차</v>
+        <v>Loader</v>
       </c>
       <c r="D69" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E69">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F69" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G69" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H69" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I69" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J69" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K69" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P69" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R69" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S69" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2770,30 +4386,54 @@
         <v>EX167</v>
       </c>
       <c r="C70" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D70" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E70">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F70" t="str">
-        <v>예시 ATS-C</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G70" t="str">
-        <v>예시 SA-2</v>
+        <v>250kb</v>
       </c>
       <c r="H70" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (SMVCU)</v>
       </c>
       <c r="I70" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J70" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K70" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L70" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M70" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P70" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R70" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S70" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2805,30 +4445,54 @@
         <v>EX168</v>
       </c>
       <c r="C71" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D71" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E71">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F71" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G71" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H71" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I71" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J71" t="str">
         <v>hw type</v>
       </c>
       <c r="K71" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L71" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M71" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P71" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R71" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S71" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2840,30 +4504,54 @@
         <v>EX169</v>
       </c>
       <c r="C72" t="str">
-        <v>지게차</v>
+        <v>Loader</v>
       </c>
       <c r="D72" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E72">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F72" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G72" t="str">
-        <v>예시 SA-2</v>
+        <v>500kb</v>
       </c>
       <c r="H72" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I72" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J72" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K72" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L72" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M72" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P72" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R72" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S72" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2875,30 +4563,54 @@
         <v>EX170</v>
       </c>
       <c r="C73" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D73" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E73">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="F73" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G73" t="str">
-        <v>예시 SA-1</v>
+        <v>500kb</v>
       </c>
       <c r="H73" t="str">
-        <v>예시 Pedal-A</v>
+        <v>CAN (EEC2)</v>
       </c>
       <c r="I73" t="str">
-        <v>예시 Starter-A</v>
+        <v>ECU control</v>
       </c>
       <c r="J73" t="str">
         <v>CAN type</v>
       </c>
       <c r="K73" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L73" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P73" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R73" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S73" t="str">
         <v>예시 X-2</v>
       </c>
     </row>
@@ -2910,30 +4622,54 @@
         <v>EX171</v>
       </c>
       <c r="C74" t="str">
-        <v>굴삭기</v>
+        <v>Excavator</v>
       </c>
       <c r="D74" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E74">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F74" t="str">
-        <v>예시 ATS-B</v>
+        <v>DOC+DPF</v>
       </c>
       <c r="G74" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H74" t="str">
-        <v>예시 Pedal-A</v>
+        <v>Hardwire Foot</v>
       </c>
       <c r="I74" t="str">
-        <v>예시 Starter-B</v>
+        <v>VCU control</v>
       </c>
       <c r="J74" t="str">
-        <v>HW type</v>
+        <v>CAN type</v>
       </c>
       <c r="K74" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L74" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M74" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P74" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R74" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S74" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
@@ -2945,36 +4681,1476 @@
         <v>EX172</v>
       </c>
       <c r="C75" t="str">
-        <v>지게차</v>
+        <v>Loader</v>
       </c>
       <c r="D75" t="str">
-        <v>미국</v>
+        <v>NA Tier4f</v>
       </c>
       <c r="E75">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="F75" t="str">
-        <v>예시 ATS-A</v>
+        <v>DOC_SDPF</v>
       </c>
       <c r="G75" t="str">
-        <v>예시 SA-1</v>
+        <v>250kb</v>
       </c>
       <c r="H75" t="str">
-        <v>예시 Pedal-B</v>
+        <v>Hardwire Foot and Hand</v>
       </c>
       <c r="I75" t="str">
-        <v>예시 Starter-A</v>
+        <v>VCU control</v>
       </c>
       <c r="J75" t="str">
         <v>HW type</v>
       </c>
       <c r="K75" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L75" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P75" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R75" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S75" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B76" t="str">
+        <v>EX173</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D76" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E76">
+        <v>165</v>
+      </c>
+      <c r="F76" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G76" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H76" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I76" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J76" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K76" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M76" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R76" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S76" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B77" t="str">
+        <v>EX174</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D77" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E77">
+        <v>135</v>
+      </c>
+      <c r="F77" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G77" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H77" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I77" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J77" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K77" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M77" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R77" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S77" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B78" t="str">
+        <v>EX175</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D78" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E78">
+        <v>260</v>
+      </c>
+      <c r="F78" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G78" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H78" t="str">
+        <v>CAN (TSC1)</v>
+      </c>
+      <c r="I78" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J78" t="str">
+        <v>CAN type</v>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R78" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S78" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B79" t="str">
+        <v>EX176</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D79" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E79">
+        <v>105</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G79" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H79" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I79" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J79" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K79" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M79" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R79" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S79" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B80" t="str">
+        <v>EX177</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D80" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E80">
+        <v>180</v>
+      </c>
+      <c r="F80" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G80" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H80" t="str">
+        <v>CAN (EEC2)</v>
+      </c>
+      <c r="I80" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J80" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="K80" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M80" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R80" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S80" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B81" t="str">
+        <v>EX178</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D81" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E81">
+        <v>340</v>
+      </c>
+      <c r="F81" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G81" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H81" t="str">
+        <v>CAN (TSC1)</v>
+      </c>
+      <c r="I81" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J81" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R81" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S81" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B82" t="str">
+        <v>EX179</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D82" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E82">
+        <v>135</v>
+      </c>
+      <c r="F82" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G82" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H82" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I82" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J82" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K82" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R82" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S82" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B83" t="str">
+        <v>EX180</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D83" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E83">
+        <v>180</v>
+      </c>
+      <c r="F83" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G83" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H83" t="str">
+        <v>CAN (EEC2)</v>
+      </c>
+      <c r="I83" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J83" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K83" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M83" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R83" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S83" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B84" t="str">
+        <v>EX181</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D84" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E84">
+        <v>240</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G84" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Hardwire Foot and Hand</v>
+      </c>
+      <c r="I84" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J84" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M84" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R84" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S84" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B85" t="str">
+        <v>EX182</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D85" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E85">
+        <v>135</v>
+      </c>
+      <c r="F85" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G85" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H85" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I85" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J85" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K85" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R85" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S85" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B86" t="str">
+        <v>EX183</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Excavator</v>
+      </c>
+      <c r="D86" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E86">
+        <v>105</v>
+      </c>
+      <c r="F86" t="str">
+        <v>DOC+DPF</v>
+      </c>
+      <c r="G86" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H86" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="I86" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J86" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K86" t="str">
+        <v>CAN (SMVCU)</v>
+      </c>
+      <c r="L86" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="P86" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R86" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S86" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>예시고객사 G</v>
+      </c>
+      <c r="B87" t="str">
+        <v>EX184</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D87" t="str">
+        <v>EU Stage3A</v>
+      </c>
+      <c r="E87">
+        <v>320</v>
+      </c>
+      <c r="F87" t="str">
+        <v>DOC+DPF</v>
+      </c>
+      <c r="G87" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H87" t="str">
+        <v>CAN (TSC1)</v>
+      </c>
+      <c r="I87" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J87" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="P87" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R87" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S87" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B88" t="str">
+        <v>EX185</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E88">
+        <v>70</v>
+      </c>
+      <c r="F88" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G88" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I88" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J88" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R88" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S88" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B89" t="str">
+        <v>EX186</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E89">
+        <v>80</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G89" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I89" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J89" t="str">
+        <v>hw type</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Hardwire (Normally closed)</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M89" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R89" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S89" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B90" t="str">
+        <v>EX187</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E90">
+        <v>360</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G90" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Hardwire Foot and Hand</v>
+      </c>
+      <c r="I90" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J90" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R90" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S90" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B91" t="str">
+        <v>EX188</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E91">
+        <v>80</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G91" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I91" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J91" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M91" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R91" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S91" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B92" t="str">
+        <v>EX189</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E92">
+        <v>80</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G92" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H92" t="str">
+        <v>CAN (EEC2)</v>
+      </c>
+      <c r="I92" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J92" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K92" t="str">
+        <v>CAN (CCVS)</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R92" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S92" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B93" t="str">
+        <v>EX190</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E93">
+        <v>220</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G93" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H93" t="str">
+        <v>CAN (TSC1)</v>
+      </c>
+      <c r="I93" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J93" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R93" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S93" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B94" t="str">
+        <v>EX191</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E94">
+        <v>60</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G94" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I94" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J94" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L94" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R94" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S94" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B95" t="str">
+        <v>EX192</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E95">
+        <v>50</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G95" t="str">
+        <v>500kb</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I95" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J95" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R95" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S95" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B96" t="str">
+        <v>EX193</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E96">
+        <v>380</v>
+      </c>
+      <c r="F96" t="str">
+        <v>DOC</v>
+      </c>
+      <c r="G96" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Hardwire Foot and Hand</v>
+      </c>
+      <c r="I96" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J96" t="str">
+        <v>CAN type</v>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R96" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S96" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B97" t="str">
+        <v>EX194</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E97">
+        <v>50</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G97" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I97" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J97" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M97" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="R97" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="S97" t="str">
+        <v>예시 X-2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B98" t="str">
+        <v>EX195</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Forklift</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E98">
+        <v>40</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G98" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Hardwire Foot</v>
+      </c>
+      <c r="I98" t="str">
+        <v>ECU control</v>
+      </c>
+      <c r="J98" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Hardwire (Normally open)</v>
+      </c>
+      <c r="L98" t="str">
+        <v>CAN</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R98" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S98" t="str">
+        <v>예시 X-1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>예시고객사 H</v>
+      </c>
+      <c r="B99" t="str">
+        <v>EX196</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Unregulated</v>
+      </c>
+      <c r="E99">
+        <v>360</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Muffler</v>
+      </c>
+      <c r="G99" t="str">
+        <v>250kb</v>
+      </c>
+      <c r="H99" t="str">
+        <v>CAN (TSC1)</v>
+      </c>
+      <c r="I99" t="str">
+        <v>VCU control</v>
+      </c>
+      <c r="J99" t="str">
+        <v>HW type</v>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Hardwire</v>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v>ECU</v>
+      </c>
+      <c r="R99" t="str">
+        <v>VCU</v>
+      </c>
+      <c r="S99" t="str">
         <v>예시 X-1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S99"/>
   </ignoredErrors>
 </worksheet>
 </file>